--- a/data/orders.xlsx
+++ b/data/orders.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2139,6 +2139,834 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>24.12.2025</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>23:14:49</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G48" t="n">
+        <v>27300</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>25.12.2025</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>18:37:14</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Oq + yod poket</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>998900601102</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G49" t="n">
+        <v>404250</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>31.12.2025</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>12:37:58</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Oq yevreka</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>+998916141120</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G50" t="n">
+        <v>81000</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>31.12.2025</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>12:38:45</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Oq + oq yevreka poket</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>+998906231120</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>9</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1665000</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20.01.2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>09:47:22</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>+998901234567</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>50.424</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3277560</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>09.02.2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>21:54:13</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Oq qalampir</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4320</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>18:50:11</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2096250</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>18:50:11</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2096250</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>18:56:41</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="G56" t="n">
+        <v>63375</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>18:56:41</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="G57" t="n">
+        <v>63375</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>18:58:28</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>998997850771</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>4.707</v>
+      </c>
+      <c r="G58" t="n">
+        <v>305955</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>18:58:28</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>998997850771</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>4.707</v>
+      </c>
+      <c r="G59" t="n">
+        <v>305955</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>19:08:32</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>998997850771</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1.721</v>
+      </c>
+      <c r="G60" t="n">
+        <v>111865</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>19:08:32</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>998997850771</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1.721</v>
+      </c>
+      <c r="G61" t="n">
+        <v>111865</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>08:23:45</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Oq oyna</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>+998900601120</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>8.638</v>
+      </c>
+      <c r="G62" t="n">
+        <v>475090</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>08:23:45</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Oq oyna</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>+998900601120</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>8.638</v>
+      </c>
+      <c r="G63" t="n">
+        <v>475090</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>13:28:31</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Qora (Seriy) oyna</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="G64" t="n">
+        <v>24150</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>13:28:31</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Qora (Seriy) oyna</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="G65" t="n">
+        <v>24150</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>14:26:03</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Oq oyna</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="G66" t="n">
+        <v>365750</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>14:26:53</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Seriy yevreka</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2015000</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>14:59:21</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Qora (Seriy) oyna</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>+998900601102</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>112500</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Yod oyna</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>+998771689119</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="G69" t="n">
+        <v>65390</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>12.03.2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10:43:34</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Oq qalampir</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>+998771689119</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>135000</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
